--- a/e2e-data/01-tenant-config-import/tb-tenant-config-package-test.xlsx
+++ b/e2e-data/01-tenant-config-import/tb-tenant-config-package-test.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -579,6 +579,11 @@
           <t>description</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>timezone</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -677,6 +682,11 @@
           <t>每日1点导入交易流水</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -773,6 +783,11 @@
       <c r="T3" s="3" t="inlineStr">
         <is>
           <t>每日6:30生成对账单</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
         </is>
       </c>
     </row>
@@ -857,6 +872,11 @@
           <t>每日7点对账</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -953,6 +973,11 @@
       <c r="T5" t="inlineStr">
         <is>
           <t>DISPATCH 全链 6-stage 覆盖样本</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1803,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>sftpReceiveStep</t>
+          <t>IMPORT_RECEIVE</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -1832,7 +1857,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>txnPreprocessStep</t>
+          <t>IMPORT_PREPROCESS</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -1886,7 +1911,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>txnValidateStep</t>
+          <t>IMPORT_VALIDATE</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1940,7 +1965,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>shardedJdbcLoadStep</t>
+          <t>IMPORT_LOAD</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1994,7 +2019,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>statementGenerateStep</t>
+          <t>EXPORT_GENERATE</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2040,7 +2065,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>TRANSFER</t>
+          <t>STORE</t>
         </is>
       </c>
       <c r="F7" s="3" t="n">
@@ -2048,7 +2073,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>encryptedOssTransferStep</t>
+          <t>EXPORT_STORE</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -2102,7 +2127,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>dispatchPrepareStep</t>
+          <t>DISPATCH_PREPARE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2156,7 +2181,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>dispatchSendStep</t>
+          <t>DISPATCH_DISPATCH</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2210,7 +2235,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>dispatchAckStep</t>
+          <t>DISPATCH_ACK</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2264,7 +2289,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>dispatchRetryStep</t>
+          <t>DISPATCH_RETRY</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2318,7 +2343,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>dispatchCompensateStep</t>
+          <t>DISPATCH_COMPENSATE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2372,7 +2397,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>dispatchCompleteStep</t>
+          <t>DISPATCH_COMPLETE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">

--- a/e2e-data/01-tenant-config-import/tb-tenant-config-package-test.xlsx
+++ b/e2e-data/01-tenant-config-import/tb-tenant-config-package-test.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resource_queue" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="business_calendar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="batch_window" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="job_definition" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_channel_config" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="file_template_config" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_definition" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pipeline_step_definition" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_definition" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_node" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="workflow_edge" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="resource_queue" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="business_calendar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="batch_window" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="job_definition" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="file_channel_config" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="file_template_config" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="pipeline_definition" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="pipeline_step_definition" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="workflow_definition" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="workflow_node" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="workflow_edge" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -729,7 +729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -968,6 +968,114 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tb</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TB_WF_RECONCILE</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>开始</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>tb</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TB_WF_RECONCILE</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>结束</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -979,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1065,6 +1173,76 @@
       </c>
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tb</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>TB_WF_RECONCILE</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>NODE_IMPORT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>tb</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>TB_WF_RECONCILE</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NODE_EXPORT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1350,7 +1528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:W5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1376,380 +1554,406 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tenant_id</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>job_code</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>job_name</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>job_type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>biz_type</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>queue_code</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>worker_group</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>schedule_type</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>schedule_expr</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>depends_on_job_code</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>calendar_code</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>window_code</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>retry_policy</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>retry_max_count</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>timeout_seconds</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>shard_strategy</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>execution_mode</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>watermark_field</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
         <is>
           <t>execution_handler</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>param_schema</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>default_params</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>enabled</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>tb</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>TB_IMPORT_TRANSACTION</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>交易流水导入</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>IMPORT</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>TRANSACTION</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>tb-import-queue</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>import</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>CRON</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>0 1 * * *</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0 0 1 * * ?</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>default-calendar</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>always-open</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="N2" t="n">
         <v>3</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="O2" t="n">
         <v>7200</v>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>STATIC</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>transactionImportHandler</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>每日1点导入交易流水</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>tb</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>TB_EXPORT_STATEMENT</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>对账单导出</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>EXPORT</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>STATEMENT</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>tb-export-queue</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>export</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>CRON</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>30 6 * * *</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0 30 6 * * ?</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>default-calendar</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>always-open</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>FIXED</t>
         </is>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="N3" t="n">
         <v>2</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="O3" t="n">
         <v>3600</v>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="P3" s="3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>statementExportHandler</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>每日6:30生成对账单</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>tb</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>TB_WF_RECONCILE</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>对账工作流</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>WORKFLOW</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>RECONCILE</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>CRON</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>0 7 * * *</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0 0 7 * * ?</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>default-calendar</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="O4" t="n">
         <v>14400</v>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>每日7点对账</t>
         </is>
@@ -1801,53 +2005,58 @@
           <t>0 0 8 * * ?</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>default-calendar</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>always-open</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>EXPONENTIAL</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>5</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>3600</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>FULL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>statementDispatchHandler</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>DISPATCH 全链 6-stage 覆盖样本</t>
         </is>
@@ -1964,7 +2173,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>{"host":"sftp","port":22,"username":"tb","password":"tb_pass_123","remotePath":"/inbound"}</t>
+          <t>{"sftp_host": "sftp", "sftp_port": 22, "sftp_username": "tb", "sftp_password": "tb_pass_123", "sftp_remote_path": "/inbound"}</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -2502,12 +2711,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>[{"source":"id","target":"ID"}]</t>
+          <t>[{"name":"txn_no","targetColumn":"txn_no","type":"STRING","required":true},{"name":"account_no","targetColumn":"account_no","type":"STRING","required":true},{"name":"txn_type","targetColumn":"txn_type","type":"STRING","required":true},{"name":"amount","targetColumn":"amount","type":"DECIMAL","required":true},{"name":"currency_code","targetColumn":"currency_code","type":"STRING","required":true},{"name":"txn_date","targetColumn":"txn_date","type":"DATE","required":true,"format":"yyyy-MM-dd"},{"name":"remark","targetColumn":"remark","type":"STRING"}]</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>[{"field":"id","rule":"required"}]</t>
+          <t>{"fieldRules":{"txn_no":{"required":true,"errorCode":"IMPORT_VALIDATE_REQUIRED"},"account_no":{"required":true,"errorCode":"IMPORT_VALIDATE_REQUIRED"},"txn_type":{"required":true,"errorCode":"IMPORT_VALIDATE_REQUIRED"},"amount":{"required":true,"errorCode":"IMPORT_VALIDATE_REQUIRED"},"currency_code":{"required":true,"errorCode":"IMPORT_VALIDATE_REQUIRED"},"txn_date":{"required":true,"errorCode":"IMPORT_VALIDATE_REQUIRED"}}}</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -2675,7 +2884,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>[{"source":"id","target":"ID"}]</t>
+          <t>[{"name":"id","sourceColumn":"id","header":"ID"},{"name":"tenant_id","sourceColumn":"tenant_id","header":"Tenant"},{"name":"txn_no","sourceColumn":"txn_no","header":"Txn No"},{"name":"account_no","sourceColumn":"account_no","header":"Account No"},{"name":"txn_type","sourceColumn":"txn_type","header":"Txn Type"},{"name":"amount","sourceColumn":"amount","header":"Amount","type":"DECIMAL"},{"name":"currency_code","sourceColumn":"currency_code","header":"Currency"},{"name":"txn_date","sourceColumn":"txn_date","header":"Txn Date","type":"DATE","format":"yyyy-MM-dd"},{"name":"remark","sourceColumn":"remark","header":"Remark"}]</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -2690,7 +2899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>select * from statement_export</t>
+          <t>SELECT id, tenant_id, txn_no, account_no, txn_type, amount, currency_code, txn_date, remark FROM biz.transaction WHERE tenant_id = :tenantId AND CAST(:batchNo AS text) IS NOT NULL</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -2858,7 +3067,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[{"source":"id","target":"ID"}]</t>
+          <t>[{"source":"id","target":"ID","name":"id"}]</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -3011,7 +3220,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>[{"source":"id","target":"ID"}]</t>
+          <t>[{"source":"id","target":"ID","name":"id"}]</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -3295,7 +3504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3403,7 +3612,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>sftpReceiveStep</t>
+          <t>IMPORT_RECEIVE</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -3457,7 +3666,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>txnPreprocessStep</t>
+          <t>IMPORT_PREPROCESS</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -3511,7 +3720,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>txnValidateStep</t>
+          <t>IMPORT_VALIDATE</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -3565,7 +3774,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>shardedJdbcLoadStep</t>
+          <t>IMPORT_LOAD</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -3619,7 +3828,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>statementGenerateStep</t>
+          <t>EXPORT_GENERATE</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -3645,54 +3854,54 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>TB_EXPORT_STATEMENT</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TB_DISPATCH_SETTLE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>STEP_TRANSFER</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>加密上传</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>TRANSFER</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>STEP_PREPARE</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>分发前准备</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PREPARE</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DISPATCH_PREPARE</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>300</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>encryptedOssTransferStep</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>120</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -3709,25 +3918,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>STEP_PREPARE</t>
+          <t>STEP_DISPATCH</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>分发前准备</t>
+          <t>实际下发</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PREPARE</t>
+          <t>DISPATCH</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>dispatchPrepareStep</t>
+          <t>DISPATCH_DISPATCH</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3763,25 +3972,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>STEP_DISPATCH</t>
+          <t>STEP_ACK</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>实际下发</t>
+          <t>回执确认</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DISPATCH</t>
+          <t>ACK</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>dispatchSendStep</t>
+          <t>DISPATCH_ACK</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3817,25 +4026,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>STEP_ACK</t>
+          <t>STEP_RETRY</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>回执确认</t>
+          <t>失败重试</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ACK</t>
+          <t>RETRY</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>dispatchAckStep</t>
+          <t>DISPATCH_RETRY</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3871,25 +4080,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>STEP_RETRY</t>
+          <t>STEP_COMPENSATE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>失败重试</t>
+          <t>补偿冲正</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>COMPENSATE</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>dispatchRetryStep</t>
+          <t>DISPATCH_COMPENSATE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3925,25 +4134,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STEP_COMPENSATE</t>
+          <t>STEP_COMPLETE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>补偿冲正</t>
+          <t>完结</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>COMPENSATE</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>dispatchCompensateStep</t>
+          <t>DISPATCH_COMPLETE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3963,60 +4172,6 @@
         <v>2</v>
       </c>
       <c r="L12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TB_DISPATCH_SETTLE</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>STEP_COMPLETE</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>完结</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>6</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>dispatchCompleteStep</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>300</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
